--- a/Data/Tables/SpawnersDefine.xlsx
+++ b/Data/Tables/SpawnersDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>生成物名称（可以没有）</t>
   </si>
@@ -68,6 +68,21 @@
   </si>
   <si>
     <t>Position</t>
+  </si>
+  <si>
+    <t>毛绒怪</t>
+  </si>
+  <si>
+    <t>吊死鬼的头</t>
+  </si>
+  <si>
+    <t>烛龙雕像</t>
+  </si>
+  <si>
+    <t>礼器之灵</t>
+  </si>
+  <si>
+    <t>陷阱</t>
   </si>
 </sst>
 </file>
@@ -1138,17 +1153,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F72"/>
-  <sheetFormatPr defaultColWidth="14.2916666666667" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="14.2920353982301" defaultRowHeight="12.35" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.25833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.29166666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="38.75" style="3" customWidth="1"/>
-    <col min="4" max="5" width="14.2916666666667" style="1"/>
-    <col min="6" max="6" width="41.875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="14.2916666666667" style="1"/>
+    <col min="1" max="1" width="8.25663716814159" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.29203539823009" style="3" customWidth="1"/>
+    <col min="3" max="3" width="38.7522123893805" style="3" customWidth="1"/>
+    <col min="4" max="5" width="14.2920353982301" style="1"/>
+    <col min="6" max="6" width="41.8761061946903" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="14.2920353982301" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="3:6">
+    <row r="1" s="1" customFormat="1" ht="12.4" spans="3:6">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1162,7 +1177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="12.4" spans="1:6">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>4</v>
@@ -1180,7 +1195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="12.4" spans="1:6">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -1200,51 +1215,90 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:5">
+    <row r="4" s="2" customFormat="1" ht="12.4" spans="1:5">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:5">
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="12.4" spans="1:5">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:5">
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="12.4" spans="1:5">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:5">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="12.4" spans="1:5">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:5">
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="12.4" spans="1:5">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="E8" s="5"/>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:5">
       <c r="A9" s="2">
